--- a/data/trans_camb/IP16A06-Dificultad-trans_camb.xlsx
+++ b/data/trans_camb/IP16A06-Dificultad-trans_camb.xlsx
@@ -40,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -53,27 +53,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
     </border>
     <border>
       <left style="thin"/>
@@ -506,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -514,9 +493,6 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -531,51 +507,33 @@
           <t>Niño</t>
         </is>
       </c>
-      <c r="D1" s="3" t="n"/>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="n"/>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="H1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
     </row>
@@ -585,9 +543,6 @@
       <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
-      <c r="G3" s="2" t="n"/>
-      <c r="H3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -600,12 +555,15 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="n">
+        <v>-0.1042577760911172</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-0.4582398352726634</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-0.2768762000836739</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
@@ -614,12 +572,15 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="n">
+        <v>-1.307722191818059</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-1.910544330413751</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-1.08835606152977</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -628,12 +589,15 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>0.6390554474254714</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.5119440030981361</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.4145585416097051</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -642,12 +606,15 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="n">
+        <v>-0.1984431416791433</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>-0.5122514850660616</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>-0.3926052991320957</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
@@ -658,10 +625,9 @@
       </c>
       <c r="C8" s="6" t="inlineStr"/>
       <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr"/>
+      <c r="E8" s="6" t="n">
+        <v>-0.9034462198300321</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -672,10 +638,9 @@
       </c>
       <c r="C9" s="6" t="inlineStr"/>
       <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="6" t="inlineStr"/>
+      <c r="E9" s="6" t="n">
+        <v>1.901789333503804</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -688,12 +653,15 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n">
+        <v>-0.2949833570967979</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.3632833007212032</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.3291630443047956</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -702,12 +670,15 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="n">
+        <v>-1.457343447934986</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-2.190847015317448</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-1.171707079251811</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
@@ -716,12 +687,15 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -730,12 +704,15 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
+      <c r="C13" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -747,9 +724,6 @@
       <c r="C14" s="6" t="inlineStr"/>
       <c r="D14" s="6" t="inlineStr"/>
       <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
@@ -761,9 +735,6 @@
       <c r="C15" s="6" t="inlineStr"/>
       <c r="D15" s="6" t="inlineStr"/>
       <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -776,12 +747,15 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="n">
+        <v>-0.003112615717977118</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.009598570638643224</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -790,12 +764,13 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="n">
+        <v>-1.336130947706159</v>
+      </c>
       <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="n">
+        <v>-0.6800250232002285</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -804,12 +779,13 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="n">
+        <v>0.8770355532199715</v>
+      </c>
       <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="n">
+        <v>0.427691820303126</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -818,12 +794,13 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr"/>
+      <c r="C19" s="6" t="n">
+        <v>-0.007122709636523761</v>
+      </c>
       <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="6" t="inlineStr"/>
+      <c r="E19" s="6" t="n">
+        <v>-0.04323798050581336</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
@@ -835,9 +812,6 @@
       <c r="C20" s="6" t="inlineStr"/>
       <c r="D20" s="6" t="inlineStr"/>
       <c r="E20" s="6" t="inlineStr"/>
-      <c r="F20" s="6" t="inlineStr"/>
-      <c r="G20" s="6" t="inlineStr"/>
-      <c r="H20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
@@ -849,9 +823,6 @@
       <c r="C21" s="6" t="inlineStr"/>
       <c r="D21" s="6" t="inlineStr"/>
       <c r="E21" s="6" t="inlineStr"/>
-      <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="6" t="inlineStr"/>
-      <c r="H21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -864,12 +835,15 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
@@ -881,9 +855,6 @@
       <c r="C23" s="5" t="inlineStr"/>
       <c r="D23" s="5" t="inlineStr"/>
       <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
@@ -895,9 +866,6 @@
       <c r="C24" s="5" t="inlineStr"/>
       <c r="D24" s="5" t="inlineStr"/>
       <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
@@ -909,9 +877,6 @@
       <c r="C25" s="6" t="inlineStr"/>
       <c r="D25" s="6" t="inlineStr"/>
       <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
@@ -923,9 +888,6 @@
       <c r="C26" s="6" t="inlineStr"/>
       <c r="D26" s="6" t="inlineStr"/>
       <c r="E26" s="6" t="inlineStr"/>
-      <c r="F26" s="6" t="inlineStr"/>
-      <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
@@ -937,9 +899,6 @@
       <c r="C27" s="6" t="inlineStr"/>
       <c r="D27" s="6" t="inlineStr"/>
       <c r="E27" s="6" t="inlineStr"/>
-      <c r="F27" s="6" t="inlineStr"/>
-      <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -952,12 +911,15 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="n">
+        <v>-0.1154447616559331</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>-0.2611219052789356</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>-0.1862714294566607</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
@@ -966,12 +928,15 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
+        <v>-0.6759811793183601</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>-0.8389631980739479</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>-0.5181790835710479</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
@@ -980,12 +945,15 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="n">
+        <v>0.294744027541082</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>0.1289039836864522</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>0.106151131443876</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
@@ -994,12 +962,15 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6" t="inlineStr"/>
+      <c r="C31" s="6" t="n">
+        <v>-0.3143948769031172</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>-0.613977035032562</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>-0.4708993881570058</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
@@ -1008,12 +979,13 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr"/>
+      <c r="C32" s="6" t="n">
+        <v>-1</v>
+      </c>
       <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr"/>
+      <c r="E32" s="6" t="n">
+        <v>-0.867561680708291</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
@@ -1022,12 +994,13 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr"/>
+      <c r="C33" s="6" t="n">
+        <v>3.485388123436916</v>
+      </c>
       <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr"/>
+      <c r="E33" s="6" t="n">
+        <v>0.7592956977472737</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1037,12 +1010,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="6">
     <mergeCell ref="A22:A27"/>
     <mergeCell ref="A4:A9"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A10:A15"/>
     <mergeCell ref="A28:A33"/>
